--- a/dptest/Templates/Report Templates/Memphis templates/LGIT/OQC_Report_Memphis_MP_Z Stopper_.xlsx
+++ b/dptest/Templates/Report Templates/Memphis templates/LGIT/OQC_Report_Memphis_MP_Z Stopper_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user01\Desktop\Memphis templates (2)\Memphis templates\LGIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\JTMES\Templates\Report Templates\Memphis templates\LGIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D243D948-B21F-48EE-9A18-035C3B8F592A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FAF5AB-3844-424E-B35B-3A2573071D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
   </bookViews>
   <sheets>
     <sheet name="Waiver Summary" sheetId="5" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="Reliability Waivers" sheetId="18" r:id="rId8"/>
     <sheet name="Rev History" sheetId="19" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <definedNames>
     <definedName name="________XG2" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="________XG2" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -2268,7 +2265,7 @@
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="2" hidden="1">FAI!ㅂㅂㅂ</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="3" hidden="1">SPC!ㅂㅂㅂ</definedName>
-    <definedName name="ㅂㅂㅂ" hidden="1">[1]!ㅂㅂㅂ</definedName>
+    <definedName name="ㅂㅂㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -7186,7 +7183,12 @@
   </cellXfs>
   <cellStyles count="372">
     <cellStyle name="___CPK__" xfId="52" xr:uid="{66B5D527-70B2-400F-8B63-DFBD3372561C}"/>
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="29" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="33" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="37" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="41" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색1 10" xfId="226" xr:uid="{144ACF6C-EC76-4508-8082-1FFC5044376A}"/>
     <cellStyle name="20% - 강조색1 11" xfId="246" xr:uid="{A0133E03-4FF6-4773-83EB-E1C71755515E}"/>
     <cellStyle name="20% - 강조색1 12" xfId="266" xr:uid="{69765A4B-5601-441F-932C-239E408BA924}"/>
@@ -7202,7 +7204,6 @@
     <cellStyle name="20% - 강조색1 7" xfId="166" xr:uid="{3D432729-A8DE-423D-A1F2-8BB10728B8A7}"/>
     <cellStyle name="20% - 강조색1 8" xfId="186" xr:uid="{EA8B51F4-DF1C-4AD3-B065-82345EB025A5}"/>
     <cellStyle name="20% - 강조색1 9" xfId="206" xr:uid="{3AF2B297-8D3F-4630-89A2-074B4220D709}"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2 10" xfId="229" xr:uid="{626F9513-4C92-4F94-B200-104CF2CD402B}"/>
     <cellStyle name="20% - 강조색2 11" xfId="249" xr:uid="{26249CFF-D7A2-4344-AF21-7004B903DE59}"/>
     <cellStyle name="20% - 강조색2 12" xfId="269" xr:uid="{4C7B131D-BF00-41A3-A47F-EF7251B28828}"/>
@@ -7218,7 +7219,6 @@
     <cellStyle name="20% - 강조색2 7" xfId="169" xr:uid="{3ACEDB0C-3AB5-42A9-8A54-0171BEA68931}"/>
     <cellStyle name="20% - 강조색2 8" xfId="189" xr:uid="{92D06AA7-BD79-4A08-A0AC-19FAAE141A9A}"/>
     <cellStyle name="20% - 강조색2 9" xfId="209" xr:uid="{87FEFB61-F2A8-431E-926D-D0AA74DBDF54}"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3 10" xfId="232" xr:uid="{61651A33-B832-41AE-9EBF-C4749E3E2278}"/>
     <cellStyle name="20% - 강조색3 11" xfId="252" xr:uid="{E949058E-E0C6-4200-8EC6-DBEF142DAD18}"/>
     <cellStyle name="20% - 강조색3 12" xfId="272" xr:uid="{426D12DE-A4BE-4992-808E-7DC40B9718AD}"/>
@@ -7234,7 +7234,6 @@
     <cellStyle name="20% - 강조색3 7" xfId="172" xr:uid="{FBCAFDFA-76DB-42D8-9AFC-73132063C498}"/>
     <cellStyle name="20% - 강조색3 8" xfId="192" xr:uid="{7B7916C4-7649-4B69-BBA1-586F1F8236AC}"/>
     <cellStyle name="20% - 강조색3 9" xfId="212" xr:uid="{B05A3FC1-2BD3-4D5D-BBD1-AF122FFA97D0}"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - 강조색4 10" xfId="235" xr:uid="{D7777BE9-BACF-476F-AC89-842F95EB340A}"/>
     <cellStyle name="20% - 강조색4 11" xfId="255" xr:uid="{8CECB8CF-16A3-4C86-9941-19EB25997AC4}"/>
     <cellStyle name="20% - 강조색4 12" xfId="275" xr:uid="{11494E53-DE89-497B-B9CA-0A28AD5C723D}"/>
@@ -7250,7 +7249,6 @@
     <cellStyle name="20% - 강조색4 7" xfId="175" xr:uid="{D8023C2B-337C-4793-B1D3-453BF274B485}"/>
     <cellStyle name="20% - 강조색4 8" xfId="195" xr:uid="{8113DDBD-D399-448B-B8ED-873D89E0096A}"/>
     <cellStyle name="20% - 강조색4 9" xfId="215" xr:uid="{14FB7DB9-C519-47BE-8EC1-AA255607A88C}"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - 강조색5 10" xfId="238" xr:uid="{E411D9CE-490D-4DFD-94EE-328AACF8795E}"/>
     <cellStyle name="20% - 강조색5 11" xfId="258" xr:uid="{A182F85F-D434-4461-A92A-139E7B12C467}"/>
     <cellStyle name="20% - 강조색5 12" xfId="278" xr:uid="{EB7F973A-7A61-4F6E-A5B0-410E883B7724}"/>
@@ -7266,7 +7264,6 @@
     <cellStyle name="20% - 강조색5 7" xfId="178" xr:uid="{4E271861-0A9C-4BD9-AA4B-8EC2BC60B6CD}"/>
     <cellStyle name="20% - 강조색5 8" xfId="198" xr:uid="{065D2FA9-1C3F-4C00-BAA7-41A137662E55}"/>
     <cellStyle name="20% - 강조색5 9" xfId="218" xr:uid="{772F6110-8CBC-401D-913D-DFF9BBD2E526}"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색6 10" xfId="241" xr:uid="{A9D7E7EF-A19E-4C1A-AB1C-96A3CDA2DCD8}"/>
     <cellStyle name="20% - 강조색6 11" xfId="261" xr:uid="{8D2F71CB-6051-471E-94A7-4CAE37718795}"/>
     <cellStyle name="20% - 강조색6 12" xfId="281" xr:uid="{2976DA9E-E40C-4CBB-B753-8F3838D90FF5}"/>
@@ -7282,7 +7279,12 @@
     <cellStyle name="20% - 강조색6 7" xfId="181" xr:uid="{7F0E0991-186C-46D1-849C-F961850DAF91}"/>
     <cellStyle name="20% - 강조색6 8" xfId="201" xr:uid="{25052CED-D218-4512-8F9B-138DD7092BA0}"/>
     <cellStyle name="20% - 강조색6 9" xfId="221" xr:uid="{CE3D1595-0958-48A2-B9EE-416DA293B80D}"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="30" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="34" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="38" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="42" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색1 10" xfId="227" xr:uid="{E08ED7FC-FA6B-4FD9-A116-0BE127A8255A}"/>
     <cellStyle name="40% - 강조색1 11" xfId="247" xr:uid="{1995D369-4950-4911-8B5B-D6D1B63DABEC}"/>
     <cellStyle name="40% - 강조색1 12" xfId="267" xr:uid="{28FA5F6C-C506-48F5-972A-4BD8254ECA20}"/>
@@ -7298,7 +7300,6 @@
     <cellStyle name="40% - 강조색1 7" xfId="167" xr:uid="{1927FD0E-4BE2-4492-BB2E-1966527C7123}"/>
     <cellStyle name="40% - 강조색1 8" xfId="187" xr:uid="{534FA0DC-8F7C-49E0-9E23-7705211A8717}"/>
     <cellStyle name="40% - 강조색1 9" xfId="207" xr:uid="{3AE69E2A-7B92-4C93-BFD7-548085599299}"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - 강조색2 10" xfId="230" xr:uid="{382D258B-D946-495B-BB96-23BC5A2A4906}"/>
     <cellStyle name="40% - 강조색2 11" xfId="250" xr:uid="{BCC6833B-7F37-4366-AB03-A4189D5D1A5C}"/>
     <cellStyle name="40% - 강조색2 12" xfId="270" xr:uid="{403E36EF-A38B-4C19-8BA7-DB8475CFAFF4}"/>
@@ -7314,7 +7315,6 @@
     <cellStyle name="40% - 강조색2 7" xfId="170" xr:uid="{06D71241-9842-4FB1-92CC-B4734351DE63}"/>
     <cellStyle name="40% - 강조색2 8" xfId="190" xr:uid="{E4CD3BF1-0702-4D79-8779-88F0FB3618AE}"/>
     <cellStyle name="40% - 강조색2 9" xfId="210" xr:uid="{132DE09A-2130-4280-B94F-352BF1679BB9}"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - 강조색3 10" xfId="233" xr:uid="{5DCA0145-145D-477F-9C69-0E7D0BDAA8CE}"/>
     <cellStyle name="40% - 강조색3 11" xfId="253" xr:uid="{12DE31AC-58EA-478B-B2F8-EC3A4EF8B964}"/>
     <cellStyle name="40% - 강조색3 12" xfId="273" xr:uid="{4D7B6B2B-88B6-4009-9330-B8230883E09C}"/>
@@ -7330,7 +7330,6 @@
     <cellStyle name="40% - 강조색3 7" xfId="173" xr:uid="{31D59DE3-E49F-462A-9662-80189E92696D}"/>
     <cellStyle name="40% - 강조색3 8" xfId="193" xr:uid="{B9B7443B-9F0E-4C88-B960-D2AFA151E97E}"/>
     <cellStyle name="40% - 강조색3 9" xfId="213" xr:uid="{4A23610B-77CE-47A2-B2FB-E8C44A920724}"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - 강조색4 10" xfId="236" xr:uid="{279AACC2-5F8A-4635-BD30-C38CC99F5BBF}"/>
     <cellStyle name="40% - 강조색4 11" xfId="256" xr:uid="{9192174F-5DD8-40D2-8FBE-748F54596A66}"/>
     <cellStyle name="40% - 강조색4 12" xfId="276" xr:uid="{E7D5EA16-D63E-4C1A-AF42-E59203C3D5BE}"/>
@@ -7346,7 +7345,6 @@
     <cellStyle name="40% - 강조색4 7" xfId="176" xr:uid="{45C0AF15-E90B-4919-B72B-1328E7C285F5}"/>
     <cellStyle name="40% - 강조색4 8" xfId="196" xr:uid="{42FE4E23-137F-4281-896F-4A37A35DF536}"/>
     <cellStyle name="40% - 강조색4 9" xfId="216" xr:uid="{5FE4A7DD-4F23-4F4B-9A91-26CA02F74E9F}"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - 강조색5 10" xfId="239" xr:uid="{BA76548E-7B5B-498D-8406-8634949E5754}"/>
     <cellStyle name="40% - 강조색5 11" xfId="259" xr:uid="{424F185F-7460-4E6C-A653-EFCCE0B5C804}"/>
     <cellStyle name="40% - 강조색5 12" xfId="279" xr:uid="{F5BD1F5E-3484-4B88-A4B4-9A38BB4DB575}"/>
@@ -7362,7 +7360,6 @@
     <cellStyle name="40% - 강조색5 7" xfId="179" xr:uid="{0E855858-D7BA-4E58-A50B-DF778967EFAA}"/>
     <cellStyle name="40% - 강조색5 8" xfId="199" xr:uid="{4D7F1574-D752-49B6-892C-7686097E072D}"/>
     <cellStyle name="40% - 강조색5 9" xfId="219" xr:uid="{C3599F2D-029D-43AC-A322-099F96CB9902}"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색6 10" xfId="242" xr:uid="{E82BFB48-84FD-41B7-AB7F-3FC7DAD9B6DF}"/>
     <cellStyle name="40% - 강조색6 11" xfId="262" xr:uid="{7F222311-21F8-4F52-86D3-B6BCB9F92164}"/>
     <cellStyle name="40% - 강조색6 12" xfId="282" xr:uid="{620521F1-AF1F-4213-A635-B81EA35B4D80}"/>
@@ -7378,7 +7375,12 @@
     <cellStyle name="40% - 강조색6 7" xfId="182" xr:uid="{05CFEC58-67B0-46E3-A580-AB3F892F5F02}"/>
     <cellStyle name="40% - 강조색6 8" xfId="202" xr:uid="{3DB6A435-9D18-41C8-A80C-5CA6BC3C8EC3}"/>
     <cellStyle name="40% - 강조색6 9" xfId="222" xr:uid="{437FDFC9-C82F-4230-A465-4560C5905C74}"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="31" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="35" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="39" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="43" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색1 10" xfId="228" xr:uid="{B2CB40AD-4A4F-4918-9765-E0E0363F2909}"/>
     <cellStyle name="60% - 강조색1 11" xfId="248" xr:uid="{E4397767-24DE-4A4E-8808-6EE3AC7ADD6A}"/>
     <cellStyle name="60% - 강조색1 12" xfId="268" xr:uid="{45163B68-6E14-49BA-BFA4-ECA510354E09}"/>
@@ -7394,7 +7396,6 @@
     <cellStyle name="60% - 강조색1 7" xfId="168" xr:uid="{8212DAC3-9A02-42BE-8CA2-BF85CA1F7FF5}"/>
     <cellStyle name="60% - 강조색1 8" xfId="188" xr:uid="{C4DD9030-1D5F-45AE-A9B8-68EA671C2427}"/>
     <cellStyle name="60% - 강조색1 9" xfId="208" xr:uid="{17F085EB-9BA6-42BC-90C0-6F0174349845}"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% - 강조색2 10" xfId="231" xr:uid="{14C597ED-74A6-41A0-B9C3-84CD44CA0D59}"/>
     <cellStyle name="60% - 강조색2 11" xfId="251" xr:uid="{8C1F64DB-16E4-48E9-A735-71A04F737194}"/>
     <cellStyle name="60% - 강조색2 12" xfId="271" xr:uid="{8AF8D59B-02D0-4311-9B00-197848AD0A13}"/>
@@ -7410,7 +7411,6 @@
     <cellStyle name="60% - 강조색2 7" xfId="171" xr:uid="{54B6E76E-4A23-423C-A58F-0036EF4BD218}"/>
     <cellStyle name="60% - 강조색2 8" xfId="191" xr:uid="{CAB13629-03F9-4D57-B12A-3727FBAF4666}"/>
     <cellStyle name="60% - 강조색2 9" xfId="211" xr:uid="{A63107D2-B5A6-4F95-8B93-DE528608944A}"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40" customBuiltin="1"/>
     <cellStyle name="60% - 강조색3 10" xfId="234" xr:uid="{ED75E9BB-902D-42DB-AF09-843CCDFA3E09}"/>
     <cellStyle name="60% - 강조색3 11" xfId="254" xr:uid="{EA1454C4-3A62-4C0E-9767-7776B2D9DF0C}"/>
     <cellStyle name="60% - 강조색3 12" xfId="274" xr:uid="{758273EF-D7DF-41A3-A017-443AF2472E7F}"/>
@@ -7426,7 +7426,6 @@
     <cellStyle name="60% - 강조색3 7" xfId="174" xr:uid="{CC34085C-2DF9-4B63-BC74-48FB0D0B41C0}"/>
     <cellStyle name="60% - 강조색3 8" xfId="194" xr:uid="{92B4DA0C-F19C-4089-8BF9-BBEE225A05A5}"/>
     <cellStyle name="60% - 강조색3 9" xfId="214" xr:uid="{FB8BE683-8343-4BEB-9B06-CDF01B070856}"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 강조색4 10" xfId="237" xr:uid="{70E89AC4-5EED-43E7-9ED8-EF9FC159426C}"/>
     <cellStyle name="60% - 강조색4 11" xfId="257" xr:uid="{069866A3-60DC-46EA-9CD7-FBE3CA7D5DA3}"/>
     <cellStyle name="60% - 강조색4 12" xfId="277" xr:uid="{D7C60D16-EB4F-4F13-94C9-22FBC38F668A}"/>
@@ -7442,7 +7441,6 @@
     <cellStyle name="60% - 강조색4 7" xfId="177" xr:uid="{98FF8F1B-C298-4C4F-8370-A09AC3F2FFB8}"/>
     <cellStyle name="60% - 강조색4 8" xfId="197" xr:uid="{5C8022D0-2716-4511-BCE5-F749E9A7505F}"/>
     <cellStyle name="60% - 강조색4 9" xfId="217" xr:uid="{398F5B73-4152-4111-A6C1-88930B304A8F}"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 강조색5 10" xfId="240" xr:uid="{A4732F92-E2E7-47F7-8962-09A53158E49E}"/>
     <cellStyle name="60% - 강조색5 11" xfId="260" xr:uid="{833A5587-5E37-4DDD-A9A7-B9B835D4EEC6}"/>
     <cellStyle name="60% - 강조색5 12" xfId="280" xr:uid="{0CF639C7-E6D7-4838-8BD1-2A7DDFC35C69}"/>
@@ -7458,7 +7456,6 @@
     <cellStyle name="60% - 강조색5 7" xfId="180" xr:uid="{B8F7E0E2-4C83-4F44-B59F-356F510E044A}"/>
     <cellStyle name="60% - 강조색5 8" xfId="200" xr:uid="{6D2D570D-EC52-4E0C-B1E9-5D2AB26D118B}"/>
     <cellStyle name="60% - 강조색5 9" xfId="220" xr:uid="{922B3494-236E-4C09-974D-F60AAF6C7BE7}"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색6 10" xfId="243" xr:uid="{45C2A6A0-CD21-437A-82CA-BC3AD53B6A17}"/>
     <cellStyle name="60% - 강조색6 11" xfId="263" xr:uid="{A320767B-703A-471C-8140-F1287F2FFA6B}"/>
     <cellStyle name="60% - 강조색6 12" xfId="283" xr:uid="{089059AD-EDC4-453B-8BF0-CD3801C452E4}"/>
@@ -7492,16 +7489,24 @@
     <cellStyle name="PrePop Currency (0)" xfId="59" xr:uid="{011529D7-C760-4C88-8E9D-F1167D2FE0AB}"/>
     <cellStyle name="Text Indent A" xfId="60" xr:uid="{DBCAAEB4-FCA1-4A86-9E72-4AB119B0DF9B}"/>
     <cellStyle name="Text Indent B" xfId="61" xr:uid="{49B06124-8F30-4376-AF00-ED1364E50F8D}"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="21" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="18" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="14" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="28" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="32" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="36" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="40" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="44" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="15" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="19" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="21" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="18" builtinId="22" customBuiltin="1"/>
     <cellStyle name="나쁨 2" xfId="365" xr:uid="{4ED3288D-E3DB-4489-ADE3-90A1AB80120C}"/>
+    <cellStyle name="良い" xfId="13" builtinId="26" customBuiltin="1"/>
     <cellStyle name="메모 10" xfId="205" xr:uid="{F1E6B1A6-DFCC-43B5-938B-AC4EA38735C0}"/>
     <cellStyle name="메모 11" xfId="225" xr:uid="{96156C23-3B33-4EC6-904C-30CD9C6AE460}"/>
     <cellStyle name="메모 12" xfId="245" xr:uid="{5CB831BA-C7F1-474B-BA74-58288726F36E}"/>
@@ -7520,25 +7525,17 @@
     <cellStyle name="메모 9" xfId="185" xr:uid="{3BDA0B01-7855-47A6-943B-A22238ECF36D}"/>
     <cellStyle name="百分比 3" xfId="2" xr:uid="{D6C95A67-1C7B-404B-8CDF-2921498D764C}"/>
     <cellStyle name="백분율 2" xfId="49" xr:uid="{E41B836F-9572-4D1C-9D74-1056A2A9CD16}"/>
-    <cellStyle name="보통" xfId="15" builtinId="28" customBuiltin="1"/>
     <cellStyle name="보통 2" xfId="366" xr:uid="{7EC43471-86A2-400A-A5A9-BBBBF5CACFAD}"/>
     <cellStyle name="常规 4" xfId="5" xr:uid="{79A5A741-AEC6-8E4D-AD07-F06A72B84B5A}"/>
     <cellStyle name="常规_8364B 2009415" xfId="48" xr:uid="{0B47AFBD-263D-4B7F-B2E7-B395D86BCEE1}"/>
-    <cellStyle name="설명 텍스트" xfId="22" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="22" builtinId="53" customBuiltin="1"/>
     <cellStyle name="쉼표 [0] 2" xfId="7" xr:uid="{404A706B-A3F0-6D4E-AC76-48F566C7C22E}"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="一般 3" xfId="1" xr:uid="{CBDF56BD-CEEB-C64C-84C9-24C904CBE56D}"/>
-    <cellStyle name="입력" xfId="16" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="9" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="10" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="11" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="12" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="13" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="17" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="入力" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="204" xr:uid="{97A0A5AD-B5E0-4681-B396-4D85486E02B2}"/>
     <cellStyle name="표준 10 2" xfId="369" xr:uid="{12101C8C-6F95-6841-852A-5ABD1CC97689}"/>
     <cellStyle name="표준 11" xfId="224" xr:uid="{DCBD210C-C26C-487C-AAFF-E96EFCCBF417}"/>
@@ -7661,26 +7658,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1213 Zs"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="ㅂㅂㅂ"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7718,7 +7699,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7824,7 +7805,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7966,7 +7947,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7976,19 +7957,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A681568-1FAC-2B47-9C47-A4A560421BB4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:J53"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="16"/>
-    <col min="2" max="2" width="13.81640625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="16" customWidth="1"/>
-    <col min="4" max="5" width="25.81640625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" style="16"/>
-    <col min="8" max="9" width="10.81640625" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="10.81640625" style="16"/>
+    <col min="1" max="1" width="10.77734375" style="16"/>
+    <col min="2" max="2" width="13.77734375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" style="16" customWidth="1"/>
+    <col min="4" max="5" width="25.77734375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="16"/>
+    <col min="8" max="9" width="10.77734375" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="16"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="1:10" ht="40.15" customHeight="1">
       <c r="A2" s="9"/>
       <c r="B2" s="164" t="s">
         <v>20</v>
@@ -8002,7 +7983,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="16.2" customHeight="1">
+    <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -8014,7 +7995,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="16.2" customHeight="1">
+    <row r="4" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="12" t="s">
@@ -8030,7 +8011,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -8048,7 +8029,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="16.2" customHeight="1">
+    <row r="6" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -8538,16 +8519,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E15028-B29C-B64B-87D8-5E0B4DDE55A4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="2" width="17.6328125" style="74" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="74" customWidth="1"/>
-    <col min="4" max="4" width="40.6328125" style="74" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="74" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="74" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="75" customWidth="1"/>
-    <col min="8" max="9" width="12.6328125" style="74" customWidth="1"/>
-    <col min="10" max="16384" width="10.90625" style="74"/>
+    <col min="1" max="2" width="17.6640625" style="74" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="74" customWidth="1"/>
+    <col min="4" max="4" width="40.6640625" style="74" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="74" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="74" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="75" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" style="74" customWidth="1"/>
+    <col min="10" max="16384" width="10.88671875" style="74"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8579,7 +8560,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.2" customHeight="1">
+    <row r="2" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A2" s="145" t="s">
         <v>143</v>
       </c>
@@ -8651,20 +8632,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5FD790-95F8-3D42-B752-B4A6DBB3509E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:V84"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="23" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="23" customWidth="1"/>
     <col min="2" max="2" width="9" style="23" customWidth="1"/>
     <col min="3" max="3" width="13" style="23" customWidth="1"/>
     <col min="4" max="6" width="9" style="23" customWidth="1"/>
     <col min="7" max="8" width="9" style="23" hidden="1" customWidth="1"/>
     <col min="9" max="20" width="9" style="23" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" style="23" customWidth="1"/>
-    <col min="22" max="22" width="12.453125" style="157"/>
-    <col min="23" max="16384" width="12.453125" style="23"/>
+    <col min="21" max="21" width="13.77734375" style="23" customWidth="1"/>
+    <col min="22" max="22" width="12.44140625" style="157"/>
+    <col min="23" max="16384" width="12.44140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21">
+    <row r="1" spans="1:21" ht="20.25">
       <c r="A1" s="167" t="s">
         <v>25</v>
       </c>
@@ -8689,7 +8670,7 @@
       <c r="T1" s="167"/>
       <c r="U1" s="167"/>
     </row>
-    <row r="2" spans="1:21" ht="10.199999999999999" customHeight="1">
+    <row r="2" spans="1:21" ht="10.15" customHeight="1">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -14025,35 +14006,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A5A5CA-E251-C049-A2A7-08038324BBE3}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:BP145"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="16" customWidth="1"/>
     <col min="4" max="4" width="24" style="16" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="16" customWidth="1"/>
-    <col min="6" max="7" width="8.1796875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="7.81640625" style="16" customWidth="1"/>
-    <col min="12" max="13" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="0.81640625" style="16" customWidth="1"/>
-    <col min="15" max="18" width="7.81640625" style="16" customWidth="1"/>
-    <col min="19" max="24" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="7.81640625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="16" customWidth="1"/>
+    <col min="6" max="7" width="8.21875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="7.77734375" style="16" customWidth="1"/>
+    <col min="12" max="13" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="0.77734375" style="16" customWidth="1"/>
+    <col min="15" max="18" width="7.77734375" style="16" customWidth="1"/>
+    <col min="19" max="24" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="7.77734375" style="16" customWidth="1"/>
     <col min="26" max="26" width="10" style="16" hidden="1" customWidth="1"/>
-    <col min="27" max="29" width="9.453125" style="16" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="7.81640625" style="16" customWidth="1"/>
+    <col min="27" max="29" width="9.44140625" style="16" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="7.77734375" style="16" customWidth="1"/>
     <col min="31" max="31" width="9" style="16" customWidth="1"/>
-    <col min="32" max="32" width="8.6328125" style="16" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" style="16" customWidth="1"/>
     <col min="33" max="34" width="9" style="16" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="7.54296875" style="16" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="0.81640625" style="16" customWidth="1"/>
-    <col min="37" max="68" width="7.81640625" style="16" customWidth="1"/>
-    <col min="69" max="16384" width="8.81640625" style="16"/>
+    <col min="35" max="35" width="7.5546875" style="16" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="0.77734375" style="16" customWidth="1"/>
+    <col min="37" max="68" width="7.77734375" style="16" customWidth="1"/>
+    <col min="69" max="16384" width="8.77734375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" s="77" customFormat="1" ht="22.2" customHeight="1">
+    <row r="1" spans="1:68" s="77" customFormat="1" ht="22.15" customHeight="1">
       <c r="A1" s="167" t="s">
         <v>52</v>
       </c>
@@ -14209,7 +14190,7 @@
       <c r="BO3" s="184"/>
       <c r="BP3" s="185"/>
     </row>
-    <row r="4" spans="1:68" s="23" customFormat="1" ht="25.2" customHeight="1">
+    <row r="4" spans="1:68" s="23" customFormat="1" ht="25.15" customHeight="1">
       <c r="A4" s="80"/>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -14291,7 +14272,7 @@
       <c r="BO4" s="187"/>
       <c r="BP4" s="188"/>
     </row>
-    <row r="5" spans="1:68" s="111" customFormat="1" ht="22.8">
+    <row r="5" spans="1:68" s="111" customFormat="1" ht="24">
       <c r="A5" s="97"/>
       <c r="B5" s="98" t="s">
         <v>62</v>
@@ -14421,7 +14402,7 @@
       <c r="BO5" s="110"/>
       <c r="BP5" s="110"/>
     </row>
-    <row r="6" spans="1:68" ht="19.2" customHeight="1">
+    <row r="6" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B6" s="112" t="s">
         <v>86</v>
       </c>
@@ -14566,7 +14547,7 @@
       <c r="BO6" s="144"/>
       <c r="BP6" s="144"/>
     </row>
-    <row r="7" spans="1:68" ht="19.2" customHeight="1">
+    <row r="7" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B7" s="112" t="s">
         <v>88</v>
       </c>
@@ -14711,7 +14692,7 @@
       <c r="BO7" s="144"/>
       <c r="BP7" s="144"/>
     </row>
-    <row r="8" spans="1:68" ht="19.2" customHeight="1">
+    <row r="8" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B8" s="112" t="s">
         <v>88</v>
       </c>
@@ -14856,7 +14837,7 @@
       <c r="BO8" s="144"/>
       <c r="BP8" s="144"/>
     </row>
-    <row r="9" spans="1:68" ht="19.2" customHeight="1">
+    <row r="9" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B9" s="112" t="s">
         <v>88</v>
       </c>
@@ -15001,7 +14982,7 @@
       <c r="BO9" s="144"/>
       <c r="BP9" s="144"/>
     </row>
-    <row r="10" spans="1:68" ht="19.2" customHeight="1">
+    <row r="10" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B10" s="112" t="s">
         <v>88</v>
       </c>
@@ -15146,7 +15127,7 @@
       <c r="BO10" s="144"/>
       <c r="BP10" s="144"/>
     </row>
-    <row r="11" spans="1:68" ht="19.2" customHeight="1">
+    <row r="11" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B11" s="112" t="s">
         <v>89</v>
       </c>
@@ -15291,7 +15272,7 @@
       <c r="BO11" s="144"/>
       <c r="BP11" s="144"/>
     </row>
-    <row r="12" spans="1:68" ht="19.2" customHeight="1">
+    <row r="12" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B12" s="112" t="s">
         <v>89</v>
       </c>
@@ -15436,7 +15417,7 @@
       <c r="BO12" s="144"/>
       <c r="BP12" s="144"/>
     </row>
-    <row r="13" spans="1:68" ht="19.2" customHeight="1">
+    <row r="13" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B13" s="112" t="s">
         <v>90</v>
       </c>
@@ -15581,7 +15562,7 @@
       <c r="BO13" s="144"/>
       <c r="BP13" s="144"/>
     </row>
-    <row r="14" spans="1:68" ht="19.2" customHeight="1">
+    <row r="14" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B14" s="112" t="s">
         <v>90</v>
       </c>
@@ -15726,7 +15707,7 @@
       <c r="BO14" s="144"/>
       <c r="BP14" s="144"/>
     </row>
-    <row r="15" spans="1:68" ht="19.2" customHeight="1">
+    <row r="15" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B15" s="112" t="s">
         <v>91</v>
       </c>
@@ -15871,7 +15852,7 @@
       <c r="BO15" s="144"/>
       <c r="BP15" s="144"/>
     </row>
-    <row r="16" spans="1:68" ht="19.2" customHeight="1">
+    <row r="16" spans="1:68" ht="19.149999999999999" customHeight="1">
       <c r="B16" s="112" t="s">
         <v>91</v>
       </c>
@@ -16016,7 +15997,7 @@
       <c r="BO16" s="144"/>
       <c r="BP16" s="144"/>
     </row>
-    <row r="17" spans="2:68" ht="19.2" customHeight="1">
+    <row r="17" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B17" s="112" t="s">
         <v>91</v>
       </c>
@@ -16161,7 +16142,7 @@
       <c r="BO17" s="144"/>
       <c r="BP17" s="144"/>
     </row>
-    <row r="18" spans="2:68" ht="19.2" customHeight="1">
+    <row r="18" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B18" s="112" t="s">
         <v>91</v>
       </c>
@@ -16306,7 +16287,7 @@
       <c r="BO18" s="144"/>
       <c r="BP18" s="144"/>
     </row>
-    <row r="19" spans="2:68" ht="19.2" customHeight="1">
+    <row r="19" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B19" s="112" t="s">
         <v>92</v>
       </c>
@@ -16451,7 +16432,7 @@
       <c r="BO19" s="144"/>
       <c r="BP19" s="144"/>
     </row>
-    <row r="20" spans="2:68" ht="19.2" customHeight="1">
+    <row r="20" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B20" s="112" t="s">
         <v>92</v>
       </c>
@@ -16596,7 +16577,7 @@
       <c r="BO20" s="144"/>
       <c r="BP20" s="144"/>
     </row>
-    <row r="21" spans="2:68" ht="19.2" customHeight="1">
+    <row r="21" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B21" s="112" t="s">
         <v>93</v>
       </c>
@@ -16741,7 +16722,7 @@
       <c r="BO21" s="144"/>
       <c r="BP21" s="144"/>
     </row>
-    <row r="22" spans="2:68" ht="19.2" customHeight="1">
+    <row r="22" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B22" s="112" t="s">
         <v>93</v>
       </c>
@@ -16886,7 +16867,7 @@
       <c r="BO22" s="144"/>
       <c r="BP22" s="144"/>
     </row>
-    <row r="23" spans="2:68" ht="19.2" customHeight="1">
+    <row r="23" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B23" s="112" t="s">
         <v>94</v>
       </c>
@@ -17031,7 +17012,7 @@
       <c r="BO23" s="144"/>
       <c r="BP23" s="144"/>
     </row>
-    <row r="24" spans="2:68" ht="19.2" customHeight="1">
+    <row r="24" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B24" s="112" t="s">
         <v>95</v>
       </c>
@@ -17176,7 +17157,7 @@
       <c r="BO24" s="144"/>
       <c r="BP24" s="144"/>
     </row>
-    <row r="25" spans="2:68" ht="19.2" customHeight="1">
+    <row r="25" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B25" s="112" t="s">
         <v>144</v>
       </c>
@@ -17309,7 +17290,7 @@
       <c r="BO25" s="144"/>
       <c r="BP25" s="144"/>
     </row>
-    <row r="26" spans="2:68" ht="19.2" customHeight="1">
+    <row r="26" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B26" s="112" t="s">
         <v>145</v>
       </c>
@@ -17442,7 +17423,7 @@
       <c r="BO26" s="144"/>
       <c r="BP26" s="144"/>
     </row>
-    <row r="27" spans="2:68" ht="19.2" customHeight="1">
+    <row r="27" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B27" s="112" t="s">
         <v>149</v>
       </c>
@@ -17575,7 +17556,7 @@
       <c r="BO27" s="144"/>
       <c r="BP27" s="144"/>
     </row>
-    <row r="28" spans="2:68" ht="19.2" customHeight="1">
+    <row r="28" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B28" s="112" t="s">
         <v>146</v>
       </c>
@@ -17708,7 +17689,7 @@
       <c r="BO28" s="144"/>
       <c r="BP28" s="144"/>
     </row>
-    <row r="29" spans="2:68" ht="19.2" customHeight="1">
+    <row r="29" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B29" s="112" t="s">
         <v>146</v>
       </c>
@@ -17841,7 +17822,7 @@
       <c r="BO29" s="144"/>
       <c r="BP29" s="144"/>
     </row>
-    <row r="30" spans="2:68" ht="19.2" customHeight="1">
+    <row r="30" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B30" s="112" t="s">
         <v>147</v>
       </c>
@@ -17986,7 +17967,7 @@
       <c r="BO30" s="144"/>
       <c r="BP30" s="144"/>
     </row>
-    <row r="31" spans="2:68" ht="19.2" customHeight="1">
+    <row r="31" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B31" s="112" t="s">
         <v>147</v>
       </c>
@@ -18131,7 +18112,7 @@
       <c r="BO31" s="144"/>
       <c r="BP31" s="144"/>
     </row>
-    <row r="32" spans="2:68" ht="19.2" customHeight="1">
+    <row r="32" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B32" s="112" t="s">
         <v>148</v>
       </c>
@@ -18276,7 +18257,7 @@
       <c r="BO32" s="144"/>
       <c r="BP32" s="144"/>
     </row>
-    <row r="33" spans="2:68" ht="19.2" customHeight="1">
+    <row r="33" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B33" s="112" t="s">
         <v>148</v>
       </c>
@@ -18421,7 +18402,7 @@
       <c r="BO33" s="144"/>
       <c r="BP33" s="144"/>
     </row>
-    <row r="34" spans="2:68" ht="19.2" customHeight="1">
+    <row r="34" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B34" s="112" t="s">
         <v>96</v>
       </c>
@@ -18566,7 +18547,7 @@
       <c r="BO34" s="144"/>
       <c r="BP34" s="144"/>
     </row>
-    <row r="35" spans="2:68" ht="19.2" customHeight="1">
+    <row r="35" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B35" s="112" t="s">
         <v>96</v>
       </c>
@@ -18711,7 +18692,7 @@
       <c r="BO35" s="144"/>
       <c r="BP35" s="144"/>
     </row>
-    <row r="36" spans="2:68" ht="19.2" customHeight="1">
+    <row r="36" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B36" s="112" t="s">
         <v>97</v>
       </c>
@@ -18856,7 +18837,7 @@
       <c r="BO36" s="144"/>
       <c r="BP36" s="144"/>
     </row>
-    <row r="37" spans="2:68" ht="19.2" customHeight="1">
+    <row r="37" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B37" s="128" t="s">
         <v>97</v>
       </c>
@@ -19001,7 +18982,7 @@
       <c r="BO37" s="144"/>
       <c r="BP37" s="144"/>
     </row>
-    <row r="38" spans="2:68" ht="19.2" customHeight="1">
+    <row r="38" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B38" s="130"/>
       <c r="C38" s="23"/>
       <c r="D38" s="131"/>
@@ -19072,7 +19053,7 @@
       <c r="BO38" s="142"/>
       <c r="BP38" s="142"/>
     </row>
-    <row r="39" spans="2:68" ht="19.2" customHeight="1">
+    <row r="39" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B39" s="130"/>
       <c r="C39" s="23"/>
       <c r="D39" s="131"/>
@@ -19140,7 +19121,7 @@
       <c r="BO39" s="142"/>
       <c r="BP39" s="142"/>
     </row>
-    <row r="40" spans="2:68" ht="19.2" customHeight="1">
+    <row r="40" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B40" s="130"/>
       <c r="C40" s="23"/>
       <c r="D40" s="131"/>
@@ -19208,7 +19189,7 @@
       <c r="BO40" s="142"/>
       <c r="BP40" s="142"/>
     </row>
-    <row r="41" spans="2:68" ht="19.2" customHeight="1">
+    <row r="41" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B41" s="130"/>
       <c r="C41" s="23"/>
       <c r="D41" s="131"/>
@@ -19276,7 +19257,7 @@
       <c r="BO41" s="142"/>
       <c r="BP41" s="142"/>
     </row>
-    <row r="42" spans="2:68" ht="19.2" customHeight="1">
+    <row r="42" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B42" s="130"/>
       <c r="C42" s="23"/>
       <c r="D42" s="131"/>
@@ -19344,7 +19325,7 @@
       <c r="BO42" s="142"/>
       <c r="BP42" s="142"/>
     </row>
-    <row r="43" spans="2:68" ht="19.2" customHeight="1">
+    <row r="43" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B43" s="130"/>
       <c r="C43" s="23"/>
       <c r="D43" s="131"/>
@@ -19412,7 +19393,7 @@
       <c r="BO43" s="142"/>
       <c r="BP43" s="142"/>
     </row>
-    <row r="44" spans="2:68" ht="19.2" customHeight="1">
+    <row r="44" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B44" s="130"/>
       <c r="C44" s="23"/>
       <c r="D44" s="131"/>
@@ -19480,7 +19461,7 @@
       <c r="BO44" s="142"/>
       <c r="BP44" s="142"/>
     </row>
-    <row r="45" spans="2:68" ht="19.2" customHeight="1">
+    <row r="45" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B45" s="130"/>
       <c r="C45" s="23"/>
       <c r="D45" s="131"/>
@@ -19548,7 +19529,7 @@
       <c r="BO45" s="142"/>
       <c r="BP45" s="142"/>
     </row>
-    <row r="46" spans="2:68" ht="19.2" customHeight="1">
+    <row r="46" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B46" s="130"/>
       <c r="C46" s="23"/>
       <c r="D46" s="131"/>
@@ -19616,7 +19597,7 @@
       <c r="BO46" s="142"/>
       <c r="BP46" s="142"/>
     </row>
-    <row r="47" spans="2:68" ht="19.2" customHeight="1">
+    <row r="47" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B47" s="130"/>
       <c r="C47" s="23"/>
       <c r="D47" s="131"/>
@@ -19684,7 +19665,7 @@
       <c r="BO47" s="142"/>
       <c r="BP47" s="142"/>
     </row>
-    <row r="48" spans="2:68" ht="19.2" customHeight="1">
+    <row r="48" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B48" s="130"/>
       <c r="C48" s="23"/>
       <c r="D48" s="131"/>
@@ -19752,7 +19733,7 @@
       <c r="BO48" s="142"/>
       <c r="BP48" s="142"/>
     </row>
-    <row r="49" spans="2:68" ht="19.2" customHeight="1">
+    <row r="49" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B49" s="130"/>
       <c r="C49" s="23"/>
       <c r="D49" s="131"/>
@@ -19820,7 +19801,7 @@
       <c r="BO49" s="142"/>
       <c r="BP49" s="142"/>
     </row>
-    <row r="50" spans="2:68" ht="19.2" customHeight="1">
+    <row r="50" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B50" s="130"/>
       <c r="C50" s="23"/>
       <c r="D50" s="131"/>
@@ -19888,7 +19869,7 @@
       <c r="BO50" s="142"/>
       <c r="BP50" s="142"/>
     </row>
-    <row r="51" spans="2:68" ht="19.2" customHeight="1">
+    <row r="51" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B51" s="130"/>
       <c r="C51" s="23"/>
       <c r="D51" s="131"/>
@@ -19956,7 +19937,7 @@
       <c r="BO51" s="142"/>
       <c r="BP51" s="142"/>
     </row>
-    <row r="52" spans="2:68" ht="19.2" customHeight="1">
+    <row r="52" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B52" s="130"/>
       <c r="C52" s="23"/>
       <c r="D52" s="131"/>
@@ -20024,7 +20005,7 @@
       <c r="BO52" s="142"/>
       <c r="BP52" s="142"/>
     </row>
-    <row r="53" spans="2:68" ht="19.2" customHeight="1">
+    <row r="53" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B53" s="130"/>
       <c r="C53" s="23"/>
       <c r="D53" s="131"/>
@@ -20092,7 +20073,7 @@
       <c r="BO53" s="142"/>
       <c r="BP53" s="142"/>
     </row>
-    <row r="54" spans="2:68" ht="19.2" customHeight="1">
+    <row r="54" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B54" s="130"/>
       <c r="C54" s="23"/>
       <c r="D54" s="131"/>
@@ -20160,7 +20141,7 @@
       <c r="BO54" s="142"/>
       <c r="BP54" s="142"/>
     </row>
-    <row r="55" spans="2:68" ht="19.2" customHeight="1">
+    <row r="55" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B55" s="130"/>
       <c r="C55" s="23"/>
       <c r="D55" s="131"/>
@@ -20228,7 +20209,7 @@
       <c r="BO55" s="142"/>
       <c r="BP55" s="142"/>
     </row>
-    <row r="56" spans="2:68" ht="19.2" customHeight="1">
+    <row r="56" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B56" s="130"/>
       <c r="C56" s="23"/>
       <c r="D56" s="131"/>
@@ -20296,7 +20277,7 @@
       <c r="BO56" s="142"/>
       <c r="BP56" s="142"/>
     </row>
-    <row r="57" spans="2:68" ht="19.2" customHeight="1">
+    <row r="57" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B57" s="130"/>
       <c r="C57" s="23"/>
       <c r="D57" s="131"/>
@@ -20364,7 +20345,7 @@
       <c r="BO57" s="142"/>
       <c r="BP57" s="142"/>
     </row>
-    <row r="58" spans="2:68" ht="19.2" customHeight="1">
+    <row r="58" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B58" s="130"/>
       <c r="C58" s="23"/>
       <c r="D58" s="131"/>
@@ -20432,7 +20413,7 @@
       <c r="BO58" s="142"/>
       <c r="BP58" s="142"/>
     </row>
-    <row r="59" spans="2:68" ht="19.2" customHeight="1">
+    <row r="59" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B59" s="130"/>
       <c r="C59" s="23"/>
       <c r="D59" s="131"/>
@@ -20500,7 +20481,7 @@
       <c r="BO59" s="142"/>
       <c r="BP59" s="142"/>
     </row>
-    <row r="60" spans="2:68" ht="19.2" customHeight="1">
+    <row r="60" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B60" s="130"/>
       <c r="C60" s="23"/>
       <c r="D60" s="131"/>
@@ -20568,7 +20549,7 @@
       <c r="BO60" s="142"/>
       <c r="BP60" s="142"/>
     </row>
-    <row r="61" spans="2:68" ht="19.2" customHeight="1">
+    <row r="61" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B61" s="130"/>
       <c r="C61" s="23"/>
       <c r="D61" s="131"/>
@@ -20636,7 +20617,7 @@
       <c r="BO61" s="142"/>
       <c r="BP61" s="142"/>
     </row>
-    <row r="62" spans="2:68" ht="19.2" customHeight="1">
+    <row r="62" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B62" s="130"/>
       <c r="C62" s="23"/>
       <c r="D62" s="131"/>
@@ -20704,7 +20685,7 @@
       <c r="BO62" s="142"/>
       <c r="BP62" s="142"/>
     </row>
-    <row r="63" spans="2:68" ht="19.2" customHeight="1">
+    <row r="63" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B63" s="130"/>
       <c r="C63" s="23"/>
       <c r="D63" s="131"/>
@@ -20772,7 +20753,7 @@
       <c r="BO63" s="142"/>
       <c r="BP63" s="142"/>
     </row>
-    <row r="64" spans="2:68" ht="19.2" customHeight="1">
+    <row r="64" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B64" s="130"/>
       <c r="C64" s="23"/>
       <c r="D64" s="131"/>
@@ -20840,7 +20821,7 @@
       <c r="BO64" s="142"/>
       <c r="BP64" s="142"/>
     </row>
-    <row r="65" spans="2:68" ht="19.2" customHeight="1">
+    <row r="65" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B65" s="130"/>
       <c r="C65" s="23"/>
       <c r="D65" s="131"/>
@@ -20908,7 +20889,7 @@
       <c r="BO65" s="142"/>
       <c r="BP65" s="142"/>
     </row>
-    <row r="66" spans="2:68" ht="19.2" customHeight="1">
+    <row r="66" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B66" s="130"/>
       <c r="C66" s="23"/>
       <c r="D66" s="131"/>
@@ -20976,7 +20957,7 @@
       <c r="BO66" s="142"/>
       <c r="BP66" s="142"/>
     </row>
-    <row r="67" spans="2:68" ht="19.2" customHeight="1">
+    <row r="67" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B67" s="130"/>
       <c r="C67" s="23"/>
       <c r="D67" s="131"/>
@@ -21044,7 +21025,7 @@
       <c r="BO67" s="142"/>
       <c r="BP67" s="142"/>
     </row>
-    <row r="68" spans="2:68" ht="19.2" customHeight="1">
+    <row r="68" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B68" s="130"/>
       <c r="C68" s="23"/>
       <c r="D68" s="131"/>
@@ -21112,7 +21093,7 @@
       <c r="BO68" s="142"/>
       <c r="BP68" s="142"/>
     </row>
-    <row r="69" spans="2:68" ht="19.2" customHeight="1">
+    <row r="69" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B69" s="130"/>
       <c r="C69" s="23"/>
       <c r="D69" s="131"/>
@@ -21180,7 +21161,7 @@
       <c r="BO69" s="142"/>
       <c r="BP69" s="142"/>
     </row>
-    <row r="70" spans="2:68" ht="19.2" customHeight="1">
+    <row r="70" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B70" s="130"/>
       <c r="C70" s="23"/>
       <c r="D70" s="131"/>
@@ -21248,7 +21229,7 @@
       <c r="BO70" s="142"/>
       <c r="BP70" s="142"/>
     </row>
-    <row r="71" spans="2:68" ht="19.2" customHeight="1">
+    <row r="71" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B71" s="130"/>
       <c r="C71" s="23"/>
       <c r="D71" s="131"/>
@@ -21316,7 +21297,7 @@
       <c r="BO71" s="142"/>
       <c r="BP71" s="142"/>
     </row>
-    <row r="72" spans="2:68" ht="19.2" customHeight="1">
+    <row r="72" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B72" s="130"/>
       <c r="C72" s="23"/>
       <c r="D72" s="131"/>
@@ -21384,7 +21365,7 @@
       <c r="BO72" s="142"/>
       <c r="BP72" s="142"/>
     </row>
-    <row r="73" spans="2:68" ht="19.2" customHeight="1">
+    <row r="73" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B73" s="130"/>
       <c r="C73" s="23"/>
       <c r="D73" s="131"/>
@@ -21452,7 +21433,7 @@
       <c r="BO73" s="142"/>
       <c r="BP73" s="142"/>
     </row>
-    <row r="74" spans="2:68" ht="19.2" customHeight="1">
+    <row r="74" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B74" s="130"/>
       <c r="C74" s="23"/>
       <c r="D74" s="131"/>
@@ -21520,7 +21501,7 @@
       <c r="BO74" s="142"/>
       <c r="BP74" s="142"/>
     </row>
-    <row r="75" spans="2:68" ht="19.2" customHeight="1">
+    <row r="75" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B75" s="130"/>
       <c r="C75" s="23"/>
       <c r="D75" s="131"/>
@@ -21588,7 +21569,7 @@
       <c r="BO75" s="142"/>
       <c r="BP75" s="142"/>
     </row>
-    <row r="76" spans="2:68" ht="19.2" customHeight="1">
+    <row r="76" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B76" s="130"/>
       <c r="C76" s="23"/>
       <c r="D76" s="131"/>
@@ -21656,7 +21637,7 @@
       <c r="BO76" s="142"/>
       <c r="BP76" s="142"/>
     </row>
-    <row r="77" spans="2:68" ht="19.2" customHeight="1">
+    <row r="77" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B77" s="130"/>
       <c r="C77" s="23"/>
       <c r="D77" s="131"/>
@@ -21724,7 +21705,7 @@
       <c r="BO77" s="142"/>
       <c r="BP77" s="142"/>
     </row>
-    <row r="78" spans="2:68" ht="19.2" customHeight="1">
+    <row r="78" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B78" s="130"/>
       <c r="C78" s="23"/>
       <c r="D78" s="131"/>
@@ -21792,7 +21773,7 @@
       <c r="BO78" s="142"/>
       <c r="BP78" s="142"/>
     </row>
-    <row r="79" spans="2:68" ht="19.2" customHeight="1">
+    <row r="79" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B79" s="130"/>
       <c r="C79" s="23"/>
       <c r="D79" s="131"/>
@@ -21860,7 +21841,7 @@
       <c r="BO79" s="142"/>
       <c r="BP79" s="142"/>
     </row>
-    <row r="80" spans="2:68" ht="19.2" customHeight="1">
+    <row r="80" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B80" s="130"/>
       <c r="C80" s="23"/>
       <c r="D80" s="131"/>
@@ -21928,7 +21909,7 @@
       <c r="BO80" s="142"/>
       <c r="BP80" s="142"/>
     </row>
-    <row r="81" spans="2:68" ht="19.2" customHeight="1">
+    <row r="81" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B81" s="130"/>
       <c r="C81" s="23"/>
       <c r="D81" s="131"/>
@@ -21996,7 +21977,7 @@
       <c r="BO81" s="142"/>
       <c r="BP81" s="142"/>
     </row>
-    <row r="82" spans="2:68" ht="19.2" customHeight="1">
+    <row r="82" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B82" s="130"/>
       <c r="C82" s="23"/>
       <c r="D82" s="131"/>
@@ -22064,7 +22045,7 @@
       <c r="BO82" s="142"/>
       <c r="BP82" s="142"/>
     </row>
-    <row r="83" spans="2:68" ht="19.2" customHeight="1">
+    <row r="83" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B83" s="130"/>
       <c r="C83" s="23"/>
       <c r="D83" s="131"/>
@@ -22132,7 +22113,7 @@
       <c r="BO83" s="142"/>
       <c r="BP83" s="142"/>
     </row>
-    <row r="84" spans="2:68" ht="19.2" customHeight="1">
+    <row r="84" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B84" s="130"/>
       <c r="C84" s="23"/>
       <c r="D84" s="131"/>
@@ -22200,7 +22181,7 @@
       <c r="BO84" s="142"/>
       <c r="BP84" s="142"/>
     </row>
-    <row r="85" spans="2:68" ht="19.2" customHeight="1">
+    <row r="85" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B85" s="130"/>
       <c r="C85" s="23"/>
       <c r="D85" s="131"/>
@@ -22268,7 +22249,7 @@
       <c r="BO85" s="142"/>
       <c r="BP85" s="142"/>
     </row>
-    <row r="86" spans="2:68" ht="19.2" customHeight="1">
+    <row r="86" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B86" s="130"/>
       <c r="C86" s="23"/>
       <c r="D86" s="131"/>
@@ -22336,7 +22317,7 @@
       <c r="BO86" s="142"/>
       <c r="BP86" s="142"/>
     </row>
-    <row r="87" spans="2:68" ht="19.2" customHeight="1">
+    <row r="87" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B87" s="130"/>
       <c r="C87" s="23"/>
       <c r="D87" s="131"/>
@@ -22404,7 +22385,7 @@
       <c r="BO87" s="142"/>
       <c r="BP87" s="142"/>
     </row>
-    <row r="88" spans="2:68" ht="19.2" customHeight="1">
+    <row r="88" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B88" s="130"/>
       <c r="C88" s="23"/>
       <c r="D88" s="131"/>
@@ -22472,7 +22453,7 @@
       <c r="BO88" s="142"/>
       <c r="BP88" s="142"/>
     </row>
-    <row r="89" spans="2:68" ht="19.2" customHeight="1">
+    <row r="89" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B89" s="130"/>
       <c r="C89" s="23"/>
       <c r="D89" s="131"/>
@@ -22540,7 +22521,7 @@
       <c r="BO89" s="142"/>
       <c r="BP89" s="142"/>
     </row>
-    <row r="90" spans="2:68" ht="19.2" customHeight="1">
+    <row r="90" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B90" s="130"/>
       <c r="C90" s="23"/>
       <c r="D90" s="131"/>
@@ -22608,7 +22589,7 @@
       <c r="BO90" s="142"/>
       <c r="BP90" s="142"/>
     </row>
-    <row r="91" spans="2:68" ht="19.2" customHeight="1">
+    <row r="91" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B91" s="130"/>
       <c r="C91" s="23"/>
       <c r="D91" s="131"/>
@@ -22676,7 +22657,7 @@
       <c r="BO91" s="142"/>
       <c r="BP91" s="142"/>
     </row>
-    <row r="92" spans="2:68" ht="19.2" customHeight="1">
+    <row r="92" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B92" s="130"/>
       <c r="C92" s="23"/>
       <c r="D92" s="131"/>
@@ -22744,7 +22725,7 @@
       <c r="BO92" s="142"/>
       <c r="BP92" s="142"/>
     </row>
-    <row r="93" spans="2:68" ht="19.2" customHeight="1">
+    <row r="93" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B93" s="130"/>
       <c r="C93" s="23"/>
       <c r="D93" s="131"/>
@@ -22812,7 +22793,7 @@
       <c r="BO93" s="142"/>
       <c r="BP93" s="142"/>
     </row>
-    <row r="94" spans="2:68" ht="19.2" customHeight="1">
+    <row r="94" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B94" s="130"/>
       <c r="C94" s="23"/>
       <c r="D94" s="131"/>
@@ -22880,7 +22861,7 @@
       <c r="BO94" s="142"/>
       <c r="BP94" s="142"/>
     </row>
-    <row r="95" spans="2:68" ht="19.2" customHeight="1">
+    <row r="95" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B95" s="130"/>
       <c r="C95" s="23"/>
       <c r="D95" s="131"/>
@@ -22948,7 +22929,7 @@
       <c r="BO95" s="142"/>
       <c r="BP95" s="142"/>
     </row>
-    <row r="96" spans="2:68" ht="19.2" customHeight="1">
+    <row r="96" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B96" s="130"/>
       <c r="C96" s="23"/>
       <c r="D96" s="131"/>
@@ -23016,7 +22997,7 @@
       <c r="BO96" s="142"/>
       <c r="BP96" s="142"/>
     </row>
-    <row r="97" spans="2:68" ht="19.2" customHeight="1">
+    <row r="97" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B97" s="130"/>
       <c r="C97" s="23"/>
       <c r="D97" s="131"/>
@@ -23084,7 +23065,7 @@
       <c r="BO97" s="142"/>
       <c r="BP97" s="142"/>
     </row>
-    <row r="98" spans="2:68" ht="19.2" customHeight="1">
+    <row r="98" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B98" s="130"/>
       <c r="C98" s="23"/>
       <c r="D98" s="131"/>
@@ -23152,7 +23133,7 @@
       <c r="BO98" s="142"/>
       <c r="BP98" s="142"/>
     </row>
-    <row r="99" spans="2:68" ht="19.2" customHeight="1">
+    <row r="99" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B99" s="130"/>
       <c r="C99" s="23"/>
       <c r="D99" s="131"/>
@@ -23220,7 +23201,7 @@
       <c r="BO99" s="142"/>
       <c r="BP99" s="142"/>
     </row>
-    <row r="100" spans="2:68" ht="19.2" customHeight="1">
+    <row r="100" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B100" s="130"/>
       <c r="C100" s="23"/>
       <c r="D100" s="131"/>
@@ -23288,7 +23269,7 @@
       <c r="BO100" s="142"/>
       <c r="BP100" s="142"/>
     </row>
-    <row r="101" spans="2:68" ht="19.2" customHeight="1">
+    <row r="101" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B101" s="130"/>
       <c r="C101" s="23"/>
       <c r="D101" s="131"/>
@@ -23356,7 +23337,7 @@
       <c r="BO101" s="142"/>
       <c r="BP101" s="142"/>
     </row>
-    <row r="102" spans="2:68" ht="19.2" customHeight="1">
+    <row r="102" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B102" s="130"/>
       <c r="C102" s="23"/>
       <c r="D102" s="131"/>
@@ -23424,7 +23405,7 @@
       <c r="BO102" s="142"/>
       <c r="BP102" s="142"/>
     </row>
-    <row r="103" spans="2:68" ht="19.2" customHeight="1">
+    <row r="103" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B103" s="130"/>
       <c r="C103" s="23"/>
       <c r="D103" s="131"/>
@@ -23492,7 +23473,7 @@
       <c r="BO103" s="142"/>
       <c r="BP103" s="142"/>
     </row>
-    <row r="104" spans="2:68" ht="19.2" customHeight="1">
+    <row r="104" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B104" s="130"/>
       <c r="C104" s="23"/>
       <c r="D104" s="131"/>
@@ -23560,7 +23541,7 @@
       <c r="BO104" s="142"/>
       <c r="BP104" s="142"/>
     </row>
-    <row r="105" spans="2:68" ht="19.2" customHeight="1">
+    <row r="105" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B105" s="130"/>
       <c r="C105" s="23"/>
       <c r="D105" s="131"/>
@@ -23628,7 +23609,7 @@
       <c r="BO105" s="142"/>
       <c r="BP105" s="142"/>
     </row>
-    <row r="106" spans="2:68" ht="19.2" customHeight="1">
+    <row r="106" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B106" s="130"/>
       <c r="C106" s="23"/>
       <c r="D106" s="131"/>
@@ -23696,7 +23677,7 @@
       <c r="BO106" s="142"/>
       <c r="BP106" s="142"/>
     </row>
-    <row r="107" spans="2:68" ht="19.2" customHeight="1">
+    <row r="107" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B107" s="130"/>
       <c r="C107" s="23"/>
       <c r="D107" s="131"/>
@@ -23764,7 +23745,7 @@
       <c r="BO107" s="142"/>
       <c r="BP107" s="142"/>
     </row>
-    <row r="108" spans="2:68" ht="19.2" customHeight="1">
+    <row r="108" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B108" s="130"/>
       <c r="C108" s="23"/>
       <c r="D108" s="131"/>
@@ -23832,7 +23813,7 @@
       <c r="BO108" s="142"/>
       <c r="BP108" s="142"/>
     </row>
-    <row r="109" spans="2:68" ht="19.2" customHeight="1">
+    <row r="109" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B109" s="130"/>
       <c r="C109" s="23"/>
       <c r="D109" s="131"/>
@@ -23900,7 +23881,7 @@
       <c r="BO109" s="142"/>
       <c r="BP109" s="142"/>
     </row>
-    <row r="110" spans="2:68" ht="19.2" customHeight="1">
+    <row r="110" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B110" s="130"/>
       <c r="C110" s="23"/>
       <c r="D110" s="131"/>
@@ -23968,7 +23949,7 @@
       <c r="BO110" s="142"/>
       <c r="BP110" s="142"/>
     </row>
-    <row r="111" spans="2:68" ht="19.2" customHeight="1">
+    <row r="111" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B111" s="130"/>
       <c r="C111" s="23"/>
       <c r="D111" s="131"/>
@@ -24036,7 +24017,7 @@
       <c r="BO111" s="142"/>
       <c r="BP111" s="142"/>
     </row>
-    <row r="112" spans="2:68" ht="19.2" customHeight="1">
+    <row r="112" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B112" s="130"/>
       <c r="C112" s="23"/>
       <c r="D112" s="131"/>
@@ -24104,7 +24085,7 @@
       <c r="BO112" s="142"/>
       <c r="BP112" s="142"/>
     </row>
-    <row r="113" spans="2:68" ht="19.2" customHeight="1">
+    <row r="113" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B113" s="130"/>
       <c r="C113" s="23"/>
       <c r="D113" s="131"/>
@@ -24172,7 +24153,7 @@
       <c r="BO113" s="142"/>
       <c r="BP113" s="142"/>
     </row>
-    <row r="114" spans="2:68" ht="19.2" customHeight="1">
+    <row r="114" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B114" s="130"/>
       <c r="C114" s="23"/>
       <c r="D114" s="131"/>
@@ -24240,7 +24221,7 @@
       <c r="BO114" s="142"/>
       <c r="BP114" s="142"/>
     </row>
-    <row r="115" spans="2:68" ht="19.2" customHeight="1">
+    <row r="115" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B115" s="130"/>
       <c r="C115" s="23"/>
       <c r="D115" s="131"/>
@@ -24308,7 +24289,7 @@
       <c r="BO115" s="142"/>
       <c r="BP115" s="142"/>
     </row>
-    <row r="116" spans="2:68" ht="19.2" customHeight="1">
+    <row r="116" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B116" s="130"/>
       <c r="C116" s="23"/>
       <c r="D116" s="131"/>
@@ -24376,7 +24357,7 @@
       <c r="BO116" s="142"/>
       <c r="BP116" s="142"/>
     </row>
-    <row r="117" spans="2:68" ht="19.2" customHeight="1">
+    <row r="117" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B117" s="130"/>
       <c r="C117" s="23"/>
       <c r="D117" s="131"/>
@@ -24444,7 +24425,7 @@
       <c r="BO117" s="142"/>
       <c r="BP117" s="142"/>
     </row>
-    <row r="118" spans="2:68" ht="19.2" customHeight="1">
+    <row r="118" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B118" s="130"/>
       <c r="C118" s="23"/>
       <c r="D118" s="131"/>
@@ -24512,7 +24493,7 @@
       <c r="BO118" s="142"/>
       <c r="BP118" s="142"/>
     </row>
-    <row r="119" spans="2:68" ht="19.2" customHeight="1">
+    <row r="119" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B119" s="130"/>
       <c r="C119" s="23"/>
       <c r="D119" s="131"/>
@@ -24580,7 +24561,7 @@
       <c r="BO119" s="142"/>
       <c r="BP119" s="142"/>
     </row>
-    <row r="120" spans="2:68" ht="19.2" customHeight="1">
+    <row r="120" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B120" s="130"/>
       <c r="C120" s="23"/>
       <c r="D120" s="131"/>
@@ -24648,7 +24629,7 @@
       <c r="BO120" s="142"/>
       <c r="BP120" s="142"/>
     </row>
-    <row r="121" spans="2:68" ht="19.2" customHeight="1">
+    <row r="121" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B121" s="130"/>
       <c r="C121" s="23"/>
       <c r="D121" s="131"/>
@@ -24716,7 +24697,7 @@
       <c r="BO121" s="142"/>
       <c r="BP121" s="142"/>
     </row>
-    <row r="122" spans="2:68" ht="19.2" customHeight="1">
+    <row r="122" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B122" s="130"/>
       <c r="C122" s="23"/>
       <c r="D122" s="131"/>
@@ -24784,7 +24765,7 @@
       <c r="BO122" s="142"/>
       <c r="BP122" s="142"/>
     </row>
-    <row r="123" spans="2:68" ht="19.2" customHeight="1">
+    <row r="123" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B123" s="130"/>
       <c r="C123" s="23"/>
       <c r="D123" s="131"/>
@@ -24852,7 +24833,7 @@
       <c r="BO123" s="142"/>
       <c r="BP123" s="142"/>
     </row>
-    <row r="124" spans="2:68" ht="19.2" customHeight="1">
+    <row r="124" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B124" s="130"/>
       <c r="C124" s="23"/>
       <c r="D124" s="131"/>
@@ -24920,7 +24901,7 @@
       <c r="BO124" s="142"/>
       <c r="BP124" s="142"/>
     </row>
-    <row r="125" spans="2:68" ht="19.2" customHeight="1">
+    <row r="125" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B125" s="130"/>
       <c r="C125" s="23"/>
       <c r="D125" s="131"/>
@@ -24988,7 +24969,7 @@
       <c r="BO125" s="142"/>
       <c r="BP125" s="142"/>
     </row>
-    <row r="126" spans="2:68" ht="19.2" customHeight="1">
+    <row r="126" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B126" s="130"/>
       <c r="C126" s="23"/>
       <c r="D126" s="131"/>
@@ -25056,7 +25037,7 @@
       <c r="BO126" s="142"/>
       <c r="BP126" s="142"/>
     </row>
-    <row r="127" spans="2:68" ht="19.2" customHeight="1">
+    <row r="127" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B127" s="130"/>
       <c r="C127" s="23"/>
       <c r="D127" s="131"/>
@@ -25124,7 +25105,7 @@
       <c r="BO127" s="142"/>
       <c r="BP127" s="142"/>
     </row>
-    <row r="128" spans="2:68" ht="19.2" customHeight="1">
+    <row r="128" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B128" s="130"/>
       <c r="C128" s="23"/>
       <c r="D128" s="131"/>
@@ -25192,7 +25173,7 @@
       <c r="BO128" s="142"/>
       <c r="BP128" s="142"/>
     </row>
-    <row r="129" spans="2:68" ht="19.2" customHeight="1">
+    <row r="129" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B129" s="130"/>
       <c r="C129" s="23"/>
       <c r="D129" s="131"/>
@@ -25260,7 +25241,7 @@
       <c r="BO129" s="142"/>
       <c r="BP129" s="142"/>
     </row>
-    <row r="130" spans="2:68" ht="19.2" customHeight="1">
+    <row r="130" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B130" s="130"/>
       <c r="C130" s="23"/>
       <c r="D130" s="131"/>
@@ -25328,7 +25309,7 @@
       <c r="BO130" s="142"/>
       <c r="BP130" s="142"/>
     </row>
-    <row r="131" spans="2:68" ht="19.2" customHeight="1">
+    <row r="131" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B131" s="130"/>
       <c r="C131" s="23"/>
       <c r="D131" s="131"/>
@@ -25396,7 +25377,7 @@
       <c r="BO131" s="142"/>
       <c r="BP131" s="142"/>
     </row>
-    <row r="132" spans="2:68" ht="19.2" customHeight="1">
+    <row r="132" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B132" s="130"/>
       <c r="C132" s="23"/>
       <c r="D132" s="131"/>
@@ -25464,7 +25445,7 @@
       <c r="BO132" s="142"/>
       <c r="BP132" s="142"/>
     </row>
-    <row r="133" spans="2:68" ht="19.2" customHeight="1">
+    <row r="133" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B133" s="130"/>
       <c r="C133" s="23"/>
       <c r="D133" s="131"/>
@@ -25532,7 +25513,7 @@
       <c r="BO133" s="142"/>
       <c r="BP133" s="142"/>
     </row>
-    <row r="134" spans="2:68" ht="19.2" customHeight="1">
+    <row r="134" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B134" s="130"/>
       <c r="C134" s="23"/>
       <c r="D134" s="131"/>
@@ -25600,7 +25581,7 @@
       <c r="BO134" s="142"/>
       <c r="BP134" s="142"/>
     </row>
-    <row r="135" spans="2:68" ht="19.2" customHeight="1">
+    <row r="135" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B135" s="130"/>
       <c r="C135" s="23"/>
       <c r="D135" s="131"/>
@@ -25668,7 +25649,7 @@
       <c r="BO135" s="142"/>
       <c r="BP135" s="142"/>
     </row>
-    <row r="136" spans="2:68" ht="19.2" customHeight="1">
+    <row r="136" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B136" s="130"/>
       <c r="C136" s="23"/>
       <c r="D136" s="131"/>
@@ -25736,7 +25717,7 @@
       <c r="BO136" s="142"/>
       <c r="BP136" s="142"/>
     </row>
-    <row r="137" spans="2:68" ht="19.2" customHeight="1">
+    <row r="137" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B137" s="130"/>
       <c r="C137" s="23"/>
       <c r="D137" s="131"/>
@@ -25804,7 +25785,7 @@
       <c r="BO137" s="142"/>
       <c r="BP137" s="142"/>
     </row>
-    <row r="138" spans="2:68" ht="19.2" customHeight="1">
+    <row r="138" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B138" s="130"/>
       <c r="C138" s="23"/>
       <c r="D138" s="131"/>
@@ -25872,7 +25853,7 @@
       <c r="BO138" s="142"/>
       <c r="BP138" s="142"/>
     </row>
-    <row r="139" spans="2:68" ht="19.2" customHeight="1">
+    <row r="139" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B139" s="130"/>
       <c r="C139" s="23"/>
       <c r="D139" s="131"/>
@@ -25940,7 +25921,7 @@
       <c r="BO139" s="142"/>
       <c r="BP139" s="142"/>
     </row>
-    <row r="140" spans="2:68" ht="19.2" customHeight="1">
+    <row r="140" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B140" s="130"/>
       <c r="C140" s="23"/>
       <c r="D140" s="131"/>
@@ -26008,7 +25989,7 @@
       <c r="BO140" s="142"/>
       <c r="BP140" s="142"/>
     </row>
-    <row r="141" spans="2:68" ht="19.2" customHeight="1">
+    <row r="141" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B141" s="130"/>
       <c r="C141" s="23"/>
       <c r="D141" s="131"/>
@@ -26076,7 +26057,7 @@
       <c r="BO141" s="142"/>
       <c r="BP141" s="142"/>
     </row>
-    <row r="142" spans="2:68" ht="19.2" customHeight="1">
+    <row r="142" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B142" s="130"/>
       <c r="C142" s="23"/>
       <c r="D142" s="131"/>
@@ -26144,7 +26125,7 @@
       <c r="BO142" s="142"/>
       <c r="BP142" s="142"/>
     </row>
-    <row r="143" spans="2:68" ht="19.2" customHeight="1">
+    <row r="143" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B143" s="130"/>
       <c r="C143" s="23"/>
       <c r="D143" s="131"/>
@@ -26212,7 +26193,7 @@
       <c r="BO143" s="142"/>
       <c r="BP143" s="142"/>
     </row>
-    <row r="144" spans="2:68" ht="19.2" customHeight="1">
+    <row r="144" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B144" s="130"/>
       <c r="C144" s="23"/>
       <c r="D144" s="131"/>
@@ -26280,7 +26261,7 @@
       <c r="BO144" s="142"/>
       <c r="BP144" s="142"/>
     </row>
-    <row r="145" spans="2:68" ht="19.2" customHeight="1">
+    <row r="145" spans="2:68" ht="19.149999999999999" customHeight="1">
       <c r="B145" s="130"/>
       <c r="C145" s="23"/>
       <c r="D145" s="131"/>
@@ -26394,24 +26375,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3645CC2-B2B6-BB49-BA93-FF129FBA96EC}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:R16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" style="36" customWidth="1"/>
-    <col min="4" max="5" width="30.81640625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="36" customWidth="1"/>
+    <col min="4" max="5" width="30.77734375" style="37" customWidth="1"/>
     <col min="6" max="6" width="13" style="37" customWidth="1"/>
     <col min="7" max="7" width="13" style="36" customWidth="1"/>
     <col min="8" max="13" width="13" style="37" customWidth="1"/>
-    <col min="14" max="14" width="60.81640625" style="38" customWidth="1"/>
-    <col min="15" max="15" width="60.81640625" style="37" customWidth="1"/>
-    <col min="16" max="18" width="29.81640625" style="37" customWidth="1"/>
+    <col min="14" max="14" width="60.77734375" style="38" customWidth="1"/>
+    <col min="15" max="15" width="60.77734375" style="37" customWidth="1"/>
+    <col min="16" max="18" width="29.77734375" style="37" customWidth="1"/>
     <col min="19" max="19" width="11" style="37"/>
-    <col min="20" max="20" width="27.54296875" style="37" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5546875" style="37" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="11" style="37"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:18" ht="40.15" customHeight="1">
       <c r="B2" s="34" t="s">
         <v>98</v>
       </c>
@@ -26427,7 +26408,7 @@
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
     </row>
-    <row r="4" spans="2:18" s="39" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:18" s="39" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="195" t="s">
         <v>99</v>
       </c>
@@ -26450,7 +26431,7 @@
       <c r="Q4" s="196"/>
       <c r="R4" s="196"/>
     </row>
-    <row r="5" spans="2:18" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:18" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="194" t="s">
         <v>100</v>
       </c>
@@ -26493,7 +26474,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="2:18" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:18" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="194"/>
       <c r="C6" s="194"/>
       <c r="D6" s="194"/>
@@ -26528,7 +26509,7 @@
       <c r="Q6" s="194"/>
       <c r="R6" s="194"/>
     </row>
-    <row r="7" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="42">
         <v>1</v>
       </c>
@@ -26549,7 +26530,7 @@
       <c r="Q7" s="49"/>
       <c r="R7" s="49"/>
     </row>
-    <row r="8" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="42">
         <v>2</v>
       </c>
@@ -26570,7 +26551,7 @@
       <c r="Q8" s="49"/>
       <c r="R8" s="49"/>
     </row>
-    <row r="9" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="42">
         <v>3</v>
       </c>
@@ -26591,7 +26572,7 @@
       <c r="Q9" s="49"/>
       <c r="R9" s="49"/>
     </row>
-    <row r="10" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="42">
         <v>4</v>
       </c>
@@ -26612,7 +26593,7 @@
       <c r="Q10" s="49"/>
       <c r="R10" s="49"/>
     </row>
-    <row r="11" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="42">
         <v>5</v>
       </c>
@@ -26633,7 +26614,7 @@
       <c r="Q11" s="49"/>
       <c r="R11" s="49"/>
     </row>
-    <row r="12" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="12" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B12" s="42">
         <v>6</v>
       </c>
@@ -26654,7 +26635,7 @@
       <c r="Q12" s="49"/>
       <c r="R12" s="49"/>
     </row>
-    <row r="13" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="13" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B13" s="42">
         <v>7</v>
       </c>
@@ -26675,7 +26656,7 @@
       <c r="Q13" s="49"/>
       <c r="R13" s="49"/>
     </row>
-    <row r="14" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="14" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B14" s="42">
         <v>8</v>
       </c>
@@ -26696,7 +26677,7 @@
       <c r="Q14" s="49"/>
       <c r="R14" s="49"/>
     </row>
-    <row r="15" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="15" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B15" s="42">
         <v>9</v>
       </c>
@@ -26717,7 +26698,7 @@
       <c r="Q15" s="49"/>
       <c r="R15" s="49"/>
     </row>
-    <row r="16" spans="2:18" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="16" spans="2:18" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B16" s="42">
         <v>10</v>
       </c>
@@ -26764,25 +26745,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A6ECE4-C7D0-4646-95C7-E9152673DED5}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:W11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" style="37" customWidth="1"/>
-    <col min="5" max="6" width="30.81640625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="36" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="37" customWidth="1"/>
+    <col min="5" max="6" width="30.77734375" style="37" customWidth="1"/>
     <col min="7" max="8" width="13" style="37" customWidth="1"/>
     <col min="9" max="9" width="13" style="36" customWidth="1"/>
-    <col min="10" max="18" width="15.81640625" style="37" customWidth="1"/>
-    <col min="19" max="19" width="60.81640625" style="38" customWidth="1"/>
-    <col min="20" max="20" width="60.81640625" style="37" customWidth="1"/>
-    <col min="21" max="23" width="29.81640625" style="37" hidden="1" customWidth="1"/>
+    <col min="10" max="18" width="15.77734375" style="37" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" style="38" customWidth="1"/>
+    <col min="20" max="20" width="60.77734375" style="37" customWidth="1"/>
+    <col min="21" max="23" width="29.77734375" style="37" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="37"/>
-    <col min="25" max="25" width="27.54296875" style="37" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5546875" style="37" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11" style="37"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:23" ht="40.15" customHeight="1">
       <c r="B2" s="34" t="s">
         <v>119</v>
       </c>
@@ -26802,7 +26783,7 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
     </row>
-    <row r="4" spans="2:23" s="39" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:23" s="39" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="195" t="s">
         <v>99</v>
       </c>
@@ -26830,7 +26811,7 @@
       <c r="V4" s="196"/>
       <c r="W4" s="196"/>
     </row>
-    <row r="5" spans="2:23" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:23" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="194" t="s">
         <v>100</v>
       </c>
@@ -26880,7 +26861,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:23" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="194"/>
       <c r="C6" s="194"/>
       <c r="D6" s="194"/>
@@ -26928,7 +26909,7 @@
       <c r="V6" s="194"/>
       <c r="W6" s="194"/>
     </row>
-    <row r="7" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="42">
         <v>1</v>
       </c>
@@ -26954,7 +26935,7 @@
       <c r="V7" s="49"/>
       <c r="W7" s="49"/>
     </row>
-    <row r="8" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="42">
         <v>2</v>
       </c>
@@ -26980,7 +26961,7 @@
       <c r="V8" s="49"/>
       <c r="W8" s="49"/>
     </row>
-    <row r="9" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="42">
         <v>3</v>
       </c>
@@ -27003,7 +26984,7 @@
       <c r="S9" s="49"/>
       <c r="T9" s="49"/>
     </row>
-    <row r="10" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="42">
         <v>4</v>
       </c>
@@ -27026,7 +27007,7 @@
       <c r="S10" s="49"/>
       <c r="T10" s="49"/>
     </row>
-    <row r="11" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="42">
         <v>5</v>
       </c>
@@ -27076,25 +27057,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFE7474-838C-A349-ABF2-783B5DA6A5AE}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:W16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" style="37" customWidth="1"/>
-    <col min="5" max="6" width="30.81640625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="36" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="37" customWidth="1"/>
+    <col min="5" max="6" width="30.77734375" style="37" customWidth="1"/>
     <col min="7" max="8" width="13" style="37" customWidth="1"/>
     <col min="9" max="9" width="13" style="36" customWidth="1"/>
-    <col min="10" max="18" width="15.81640625" style="37" customWidth="1"/>
-    <col min="19" max="19" width="60.81640625" style="38" customWidth="1"/>
-    <col min="20" max="20" width="60.81640625" style="37" customWidth="1"/>
-    <col min="21" max="23" width="29.81640625" style="37" customWidth="1"/>
+    <col min="10" max="18" width="15.77734375" style="37" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" style="38" customWidth="1"/>
+    <col min="20" max="20" width="60.77734375" style="37" customWidth="1"/>
+    <col min="21" max="23" width="29.77734375" style="37" customWidth="1"/>
     <col min="24" max="24" width="11" style="37"/>
-    <col min="25" max="25" width="27.54296875" style="37" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5546875" style="37" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11" style="37"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:23" ht="40.15" customHeight="1">
       <c r="B2" s="34" t="s">
         <v>128</v>
       </c>
@@ -27114,7 +27095,7 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
     </row>
-    <row r="4" spans="2:23" s="39" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:23" s="39" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="195" t="s">
         <v>99</v>
       </c>
@@ -27142,7 +27123,7 @@
       <c r="V4" s="196"/>
       <c r="W4" s="196"/>
     </row>
-    <row r="5" spans="2:23" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:23" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="194" t="s">
         <v>100</v>
       </c>
@@ -27192,7 +27173,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:23" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="194"/>
       <c r="C6" s="198"/>
       <c r="D6" s="198"/>
@@ -27240,7 +27221,7 @@
       <c r="V6" s="194"/>
       <c r="W6" s="194"/>
     </row>
-    <row r="7" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="42">
         <v>1</v>
       </c>
@@ -27266,7 +27247,7 @@
       <c r="V7" s="49"/>
       <c r="W7" s="49"/>
     </row>
-    <row r="8" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="42">
         <v>2</v>
       </c>
@@ -27292,7 +27273,7 @@
       <c r="V8" s="49"/>
       <c r="W8" s="49"/>
     </row>
-    <row r="9" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="42">
         <v>3</v>
       </c>
@@ -27318,7 +27299,7 @@
       <c r="V9" s="49"/>
       <c r="W9" s="49"/>
     </row>
-    <row r="10" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="42">
         <v>4</v>
       </c>
@@ -27344,7 +27325,7 @@
       <c r="V10" s="49"/>
       <c r="W10" s="49"/>
     </row>
-    <row r="11" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="42">
         <v>5</v>
       </c>
@@ -27370,7 +27351,7 @@
       <c r="V11" s="49"/>
       <c r="W11" s="49"/>
     </row>
-    <row r="12" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="12" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B12" s="42">
         <v>6</v>
       </c>
@@ -27396,7 +27377,7 @@
       <c r="V12" s="49"/>
       <c r="W12" s="49"/>
     </row>
-    <row r="13" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="13" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B13" s="42">
         <v>7</v>
       </c>
@@ -27422,7 +27403,7 @@
       <c r="V13" s="49"/>
       <c r="W13" s="49"/>
     </row>
-    <row r="14" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="14" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B14" s="42">
         <v>8</v>
       </c>
@@ -27448,7 +27429,7 @@
       <c r="V14" s="49"/>
       <c r="W14" s="49"/>
     </row>
-    <row r="15" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="15" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B15" s="42">
         <v>9</v>
       </c>
@@ -27474,7 +27455,7 @@
       <c r="V15" s="49"/>
       <c r="W15" s="49"/>
     </row>
-    <row r="16" spans="2:23" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="16" spans="2:23" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B16" s="42">
         <v>10</v>
       </c>
@@ -27527,22 +27508,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09DFCB26-FFC5-C544-9EE3-C2A3F044085A}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:N10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="37" customWidth="1"/>
-    <col min="3" max="6" width="30.81640625" style="36" customWidth="1"/>
-    <col min="7" max="7" width="30.81640625" style="37" customWidth="1"/>
-    <col min="8" max="9" width="20.81640625" style="37" customWidth="1"/>
-    <col min="10" max="10" width="60.81640625" style="38" customWidth="1"/>
-    <col min="11" max="11" width="60.81640625" style="37" customWidth="1"/>
-    <col min="12" max="14" width="29.81640625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="37" customWidth="1"/>
+    <col min="3" max="6" width="30.77734375" style="36" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="37" customWidth="1"/>
+    <col min="8" max="9" width="20.77734375" style="37" customWidth="1"/>
+    <col min="10" max="10" width="60.77734375" style="38" customWidth="1"/>
+    <col min="11" max="11" width="60.77734375" style="37" customWidth="1"/>
+    <col min="12" max="14" width="29.77734375" style="37" customWidth="1"/>
     <col min="15" max="15" width="11" style="37"/>
-    <col min="16" max="16" width="27.54296875" style="37" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5546875" style="37" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="11" style="37"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:14" ht="40.15" customHeight="1">
       <c r="B2" s="34" t="s">
         <v>129</v>
       </c>
@@ -27562,7 +27543,7 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
     </row>
-    <row r="4" spans="2:14" s="39" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:14" s="39" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="195" t="s">
         <v>99</v>
       </c>
@@ -27581,7 +27562,7 @@
       <c r="M4" s="196"/>
       <c r="N4" s="196"/>
     </row>
-    <row r="5" spans="2:14" s="41" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:14" s="41" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="40" t="s">
         <v>100</v>
       </c>
@@ -27622,7 +27603,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="2:14" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="6" spans="2:14" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B6" s="42">
         <v>1</v>
       </c>
@@ -27639,7 +27620,7 @@
       <c r="M6" s="49"/>
       <c r="N6" s="49"/>
     </row>
-    <row r="7" spans="2:14" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:14" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="42">
         <v>2</v>
       </c>
@@ -27656,7 +27637,7 @@
       <c r="M7" s="49"/>
       <c r="N7" s="49"/>
     </row>
-    <row r="8" spans="2:14" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:14" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="42">
         <v>3</v>
       </c>
@@ -27673,7 +27654,7 @@
       <c r="M8" s="49"/>
       <c r="N8" s="49"/>
     </row>
-    <row r="9" spans="2:14" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:14" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="42">
         <v>4</v>
       </c>
@@ -27690,7 +27671,7 @@
       <c r="M9" s="49"/>
       <c r="N9" s="49"/>
     </row>
-    <row r="10" spans="2:14" s="39" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:14" s="39" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="42">
         <v>5</v>
       </c>
@@ -27721,11 +27702,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF6365C-A1FE-BC43-BC55-971EE20F1107}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:E3"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="90.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="90.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
